--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.0136518771331</v>
+      </c>
+      <c r="C2">
         <v>27.64031095942359</v>
-      </c>
-      <c r="C2">
-        <v>27.0136518771331</v>
       </c>
       <c r="D2">
         <v>3.617904304578974</v>
       </c>
       <c r="E2">
+        <v>17.46715789344629</v>
+      </c>
+      <c r="F2">
+        <v>64.6604834210962</v>
+      </c>
+      <c r="G2">
         <v>17.87235868545752</v>
-      </c>
-      <c r="F2">
-        <v>64.66048342109619</v>
-      </c>
-      <c r="G2">
-        <v>17.46715789344629</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>32.06793206793207</v>
+      </c>
+      <c r="C3">
         <v>36.8964368964369</v>
-      </c>
-      <c r="C3">
-        <v>32.06793206793207</v>
       </c>
       <c r="D3">
         <v>2.71028880866426</v>
       </c>
       <c r="E3">
-        <v>21.83681513598738</v>
+        <v>18.97910918407568</v>
       </c>
       <c r="F3">
         <v>59.18407567993692</v>
       </c>
       <c r="G3">
-        <v>18.97910918407568</v>
+        <v>21.83681513598738</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.06787330316742</v>
+      </c>
+      <c r="C4">
         <v>31.90045248868778</v>
-      </c>
-      <c r="C4">
-        <v>31.06787330316742</v>
       </c>
       <c r="D4">
         <v>3.134751773049645</v>
       </c>
       <c r="E4">
-        <v>19.5746334962239</v>
+        <v>19.06374944469125</v>
       </c>
       <c r="F4">
         <v>61.36161705908484</v>
       </c>
       <c r="G4">
-        <v>19.06374944469125</v>
+        <v>19.5746334962239</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.74798846212236</v>
+      </c>
+      <c r="C5">
         <v>30.73478062851071</v>
-      </c>
-      <c r="C5">
-        <v>29.74798846212236</v>
       </c>
       <c r="D5">
         <v>3.253642874783897</v>
       </c>
       <c r="E5">
-        <v>19.15145208589538</v>
+        <v>18.53656229306594</v>
       </c>
       <c r="F5">
         <v>62.3119856210387</v>
       </c>
       <c r="G5">
-        <v>18.53656229306594</v>
+        <v>19.15145208589538</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.76569037656904</v>
+      </c>
+      <c r="C6">
         <v>32.76150627615063</v>
-      </c>
-      <c r="C6">
-        <v>28.76569037656904</v>
       </c>
       <c r="D6">
         <v>3.052362707535121</v>
       </c>
       <c r="E6">
-        <v>20.28234684626344</v>
+        <v>17.80857401890946</v>
       </c>
       <c r="F6">
-        <v>61.9090791348271</v>
+        <v>61.90907913482709</v>
       </c>
       <c r="G6">
-        <v>17.80857401890947</v>
+        <v>20.28234684626343</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>35.35110777318813</v>
+      </c>
+      <c r="C7">
         <v>28.63687570409313</v>
-      </c>
-      <c r="C7">
-        <v>35.35110777318813</v>
       </c>
       <c r="D7">
         <v>3.492001049042749</v>
       </c>
       <c r="E7">
-        <v>17.4627891000687</v>
+        <v>21.55713304327914</v>
       </c>
       <c r="F7">
         <v>60.98007785665217</v>
       </c>
       <c r="G7">
-        <v>21.55713304327914</v>
+        <v>17.4627891000687</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>31.2938177182919</v>
+      </c>
+      <c r="C8">
         <v>33.66794136392607</v>
-      </c>
-      <c r="C8">
-        <v>31.2938177182919</v>
       </c>
       <c r="D8">
         <v>2.970184571699006</v>
       </c>
       <c r="E8">
-        <v>20.40954312759587</v>
+        <v>18.97034675939341</v>
       </c>
       <c r="F8">
         <v>60.62011011301072</v>
       </c>
       <c r="G8">
-        <v>18.97034675939341</v>
+        <v>20.40954312759587</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.92448206727556</v>
+      </c>
+      <c r="C9">
         <v>30.60815326353308</v>
-      </c>
-      <c r="C9">
-        <v>30.92448206727556</v>
       </c>
       <c r="D9">
         <v>3.267103347889374</v>
       </c>
       <c r="E9">
-        <v>18.94858781994704</v>
+        <v>19.14441747572815</v>
       </c>
       <c r="F9">
         <v>61.9069947043248</v>
       </c>
       <c r="G9">
-        <v>19.14441747572815</v>
+        <v>18.94858781994704</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.15439899866758</v>
+      </c>
+      <c r="C10">
         <v>32.95917955343805</v>
-      </c>
-      <c r="C10">
-        <v>28.15439899866758</v>
       </c>
       <c r="D10">
         <v>3.034056106823472</v>
       </c>
       <c r="E10">
-        <v>20.45710848808361</v>
+        <v>17.47487657569606</v>
       </c>
       <c r="F10">
         <v>62.06801493622034</v>
       </c>
       <c r="G10">
-        <v>17.47487657569606</v>
+        <v>20.45710848808361</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.19384872894654</v>
+      </c>
+      <c r="C11">
         <v>29.1034627053039</v>
-      </c>
-      <c r="C11">
-        <v>33.19384872894654</v>
       </c>
       <c r="D11">
         <v>3.436017253774263</v>
       </c>
       <c r="E11">
-        <v>17.93219027974732</v>
+        <v>20.45249452107774</v>
       </c>
       <c r="F11">
         <v>61.61531519917494</v>
       </c>
       <c r="G11">
-        <v>20.45249452107774</v>
+        <v>17.93219027974732</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>31.5015867713379</v>
+      </c>
+      <c r="C12">
         <v>35.69400367462836</v>
-      </c>
-      <c r="C12">
-        <v>31.5015867713379</v>
       </c>
       <c r="D12">
         <v>2.801591015442209</v>
       </c>
       <c r="E12">
+        <v>18.84115884115884</v>
+      </c>
+      <c r="F12">
+        <v>59.81018981018982</v>
+      </c>
+      <c r="G12">
         <v>21.34865134865135</v>
-      </c>
-      <c r="F12">
-        <v>59.8101898101898</v>
-      </c>
-      <c r="G12">
-        <v>18.84115884115884</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.13674560733384</v>
+      </c>
+      <c r="C13">
         <v>35.84924879042526</v>
-      </c>
-      <c r="C13">
-        <v>29.13674560733384</v>
       </c>
       <c r="D13">
         <v>2.789458729933229</v>
       </c>
       <c r="E13">
-        <v>21.7286618305294</v>
+        <v>17.66013273653342</v>
       </c>
       <c r="F13">
         <v>60.61120543293718</v>
       </c>
       <c r="G13">
-        <v>17.66013273653342</v>
+        <v>21.7286618305294</v>
       </c>
     </row>
   </sheetData>
